--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122890476</v>
+        <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>91196</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,44 +687,49 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lågan, Södermalm, Sundsvall, Mpd</t>
+          <t>Planar ut, Södermalm, Sundsvall, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619322</v>
+        <v>619313</v>
       </c>
       <c r="R2" t="n">
-        <v>6918530</v>
+        <v>6918508</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kan ev vara ring hack av tretåig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,7 +772,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -778,121 +787,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>122878131</v>
-      </c>
-      <c r="B3" t="n">
-        <v>57478</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Planar ut, Södermalm, Sundsvall, Mpd</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>619313</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6918508</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Medelpad</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Sundsvall</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-03-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Kan ev vara ring hack av tretåig</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Magnus Lilja</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Magnus Lilja</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,234 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125217701</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57666</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stigen, Östermalm, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>619475</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6918395</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125217712</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57761</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stigen, Östermalm, Sundsvall, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>619475</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6918395</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125217701</v>
+        <v>125217712</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125217712</v>
+        <v>125217701</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125217712</v>
+        <v>125217701</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125217701</v>
+        <v>125217712</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57761</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125217701</v>
+        <v>125217712</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57914</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125217712</v>
+        <v>125217701</v>
       </c>
       <c r="B4" t="n">
-        <v>57761</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -790,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125217712</v>
+        <v>125217701</v>
       </c>
       <c r="B3" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125217701</v>
+        <v>125217712</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122878131</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125217701</v>
+        <v>125217712</v>
       </c>
       <c r="B3" t="n">
-        <v>57811</v>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125217712</v>
+        <v>125217701</v>
       </c>
       <c r="B4" t="n">
-        <v>57932</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 24782-2024 artfynd.xlsx
+++ b/artfynd/A 24782-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122878131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125217712</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,8 +1015,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125217701</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>